--- a/光伏配储项目/电价数据/2026/坪石B厂.xlsx
+++ b/光伏配储项目/电价数据/2026/坪石B厂.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.51247</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38472</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.21808</v>
+      </c>
+      <c r="D117" t="n">
+        <v>1.04656</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5843400000000001</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.51419</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.9760700000000001</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43783</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.4547</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42215</v>
+      </c>
+      <c r="L117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.87944</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.8678400000000001</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39662</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40125</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42338</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41278</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39166</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38511</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41714</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39226</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42089</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.4141</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.4241</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41211</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44291</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.27439</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29976</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.31281</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>-0.03792</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>-0.04022999999999999</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.04214</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.03734000000000001</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>-0.03371</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.03556</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.04638</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.02368</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.02605</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.02516</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>-0.04901</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.04939</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.01927</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.01519</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>-0.02722</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.01928</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.0406</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.04763000000000001</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>-0.03793</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>-0.00826</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.19972</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.28388</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.5555099999999999</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.42918</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.39729</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.67945</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39566</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.56985</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.4335</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43754</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.42453</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.5661799999999999</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.44945</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.6039099999999999</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.79863</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.62762</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.63087</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.73886</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.9280900000000001</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.41449</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.6596799999999999</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.58338</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.7216900000000001</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.47325</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.37839</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.62391</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.60361</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.49976</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48061</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.44256</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41627</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42599</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.6917000000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.00223</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.63746</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.5504199999999999</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.66684</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.49368</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51746</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50461</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50492</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48685</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.4689</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37887</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37957</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.38997</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36972</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35517</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35478</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37407</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37432</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35827</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37932</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41776</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.48453</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.55198</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.49126</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42806</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.36651</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.34824</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42787</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.45051</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.26536</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.3509</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.24181</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.18925</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.17402</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30175</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.10996</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.19571</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.37425</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.23522</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.01528</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.1544</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>-0.03993</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.02113</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>-0.005650000000000001</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.13077</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.19293</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.18421</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.37309</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>-0.02031</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.01132</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>-0.04192</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.36112</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>-0.0362</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.33415</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.37302</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.42252</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.41168</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.44832</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.42807</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.43169</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.42439</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.40217</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.57847</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.48143</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.34326</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.49302</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.5881000000000001</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.53223</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.67147</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.63274</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.7192799999999999</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.43792</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.41012</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.76548</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.47084</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.46532</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.43548</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.4434</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43571</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42919</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40338</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.32275</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37638</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35521</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33471</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50979</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.42696</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.39414</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.42217</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40908</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38993</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38376</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36389</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42929</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44498</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39649</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36778</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36856</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36173</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35213</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36716</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35936</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38531</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39638</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47376</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44518</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43948</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34764</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39531</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35308</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36745</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.25999</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.25912</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.25171</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.2086</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.23232</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.27177</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.32686</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.32189</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34555</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.34632</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.40132</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.32563</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.36354</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.43849</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.41576</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.36753</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.41702</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.4387200000000001</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.46806</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.50346</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.40727</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.36399</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.4568</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.4082</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.46292</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.39568</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.45147</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.5246900000000001</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.37141</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.3814</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.34027</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.35683</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.52535</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.60862</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.57665</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.59634</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.4636</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.42249</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.48195</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.40242</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.44713</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.43637</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.45845</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.44403</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.39519</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.37436</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.41968</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.39926</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.39517</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39864</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36245</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34207</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.47628</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.35583</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38793</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38909</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39712</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36635</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38504</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38406</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45007</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35795</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34754</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36045</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35584</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.3566</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33657</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33379</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.32966</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34934</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38334</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38912</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.3727</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34327</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39207</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.36188</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.36619</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.34291</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26078</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.12537</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.24123</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.19747</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.34631</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.28189</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.20037</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30431</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.56038</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.32809</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.4014</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.21195</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.2244</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.16755</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.11039</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>-0.02609</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.03183</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>-0.0048</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.23461</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.00515</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>-0.02663</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.10153</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.19438</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.19518</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.10263</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.10124</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.1016</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.33636</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.16468</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.33211</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.37402</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.36108</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.35316</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.40092</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.44695</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.34314</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.39305</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.39248</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.39012</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41543</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.35899</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34636</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34079</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31918</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29367</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.30734</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31548</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31145</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31575</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.30338</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38219</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35548</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31667</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31689</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.3138</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31569</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.30431</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.3082</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.30188</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.3036</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.3061</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3136</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33261</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.30504</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.29928</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.2113</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.22039</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.21208</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.20636</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04475</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.21736</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.21336</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.192</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.0287</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.17798</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.09369</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.03678</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.03645</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.03838</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.03990999999999999</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.03943</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04215</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04678</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04461</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04071</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.03826</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>-0.04911</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>-0.04093</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.00818</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.03394</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09587000000000001</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29011</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29181</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38762</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39198</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38737</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37687</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39935</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39979</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40964</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46717</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39607</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39955</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41675</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34473</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35078</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36798</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.6535700000000001</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.39958</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44506</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42235</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42225</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35972</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35852</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35722</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33194</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30876</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32271</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33486</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31429</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32166</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29994</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35185</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31576</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10252</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04343</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04699</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04484</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01016</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20649</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.0494</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04396</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04563</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04371</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04337</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04550999999999999</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04341</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04527</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04539</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.0436</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04424</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.02099</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04472</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04740999999999999</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04793</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19972</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14271</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28991</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29463</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30451</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.2998</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.2949</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29326</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29222</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29675</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29072</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29495</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26873</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29379</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30372</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.3022</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34753</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36615</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36469</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.3353</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31699</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40418</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34973</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30701</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31461</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30132</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28112</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29439</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29066</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28081</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27114</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27087</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28101</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17235</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15859</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1709</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14768</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15942</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15856</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23609</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21398</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22649</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26881</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28563</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29073</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29067</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28081</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28101</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28041</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.2707</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28089</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.3049</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30937</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29748</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.3836</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42819</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45649</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41851</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41534</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38886</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40247</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.2993</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15653</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29438</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31095</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31344</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34631</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38547</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49798</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91408</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8625</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29601</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35328</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88713</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63154</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18672</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8684700000000001</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.53607</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33048</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03266</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5304099999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79067</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.52965</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7726499999999999</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7772899999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87673</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8737</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49285</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39838</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39951</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.4496</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20661</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87881</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55101</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6214700000000001</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53822</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49758</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45577</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42421</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43707</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.4499</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38807</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45267</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41976</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.3999</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36511</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38482</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41455</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.4335</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39005</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33821</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34459</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40216</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34726</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45069</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35339</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39988</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.39956</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58547</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42707</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5955900000000001</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60123</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.69026</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46852</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41754</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5802200000000001</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.40598</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.27351</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.85888</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.78138</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.78584</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.24351</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44042</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33303</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30563</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.30043</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.542</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31057</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33676</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30624</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34378</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31508</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31491</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30347</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29556</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31207</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31442</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35414</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33798</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33718</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.40951</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41213</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45168</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41447</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39113</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.3746</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.3533</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.91804</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46452</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.41954</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.40772</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.46371</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38033</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40938</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.36458</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34732</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38884</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33046</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34546</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.39959</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.49913</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35684</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38722</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34326</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35497</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37031</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36282</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31637</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.3136</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33255</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31281</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29064</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.29066</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.29753</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16613</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30444</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33196</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.31674</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.30646</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.2622</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19891</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27721</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19289</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31119</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28304</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31179</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.3527</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.03572</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31446</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.31756</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.30279</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31163</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29963</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30911</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32037</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31401</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29001</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34805</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25561</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.33723</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33721</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27645</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.33735</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38526</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.44298</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.38767</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42316</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35247</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44986</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.41996</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.4012</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.3999</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5951900000000001</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.34936</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.88971</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.45209</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.1607</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.69984</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79067</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.66438</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.57912</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.44975</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45061</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50098</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.44018</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43744</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41522</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41312</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42349</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.50032</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41312</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43435</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41268</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43448</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39055</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42776</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45012</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42375</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43386</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41312</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41315</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42324</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39881</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40243</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.4946</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29629</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36663</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.3686</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30754</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31715</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30371</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.5502899999999999</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.36365</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.30804</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24964</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.30373</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15497</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27812</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27533</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.01477</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30116</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26159</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25527</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30712</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28299</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28505</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.29037</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.2918</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30963</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31367</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32386</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.40356</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.4003</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33553</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.36805</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36214</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.36456</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36218</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34889</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5698300000000001</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46206</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.8474299999999999</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46431</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.4362799999999999</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37729</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.45662</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38517</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36821</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32334</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42161</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33809</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33459</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32429</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32429</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32308</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30861</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32459</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31469</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30914</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32409</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31651</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.31887</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.38974</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34836</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39797</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37314</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35352</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33104</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33365</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31841</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.28108</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33312</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.30886</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.2805</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.29438</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.27921</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22537</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14141</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14508</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.27992</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15272</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>-0.04725</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>-0.0205</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14129</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.13606</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.24708</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.13658</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.16726</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>-0.00627</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>-0.03706</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.10774</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.10733</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.12595</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.1357</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14056</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.27622</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.34387</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.36392</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34287</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37911</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39719</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38397</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44851</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39883</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.38979</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40053</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.3963</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45136</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.4385</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43782</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44274</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.4437</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40183</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38985</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39702</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39086</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34675</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.3482</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33864</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5371</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38843</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46756</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42276</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.4149</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36979</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38054</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3789</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37929</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36986</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38003</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39084</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.37998</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34696</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35488</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34492</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35453</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38007</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34865</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36078</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29791</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31426</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31375</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29518</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.15634</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.13915</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>-0.006730000000000001</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.2005</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30925</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.16546</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24327</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>-0.00293</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29504</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28858</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31623</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31232</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.35408</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31363</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29387</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28651</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24223</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30795</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32586</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30631</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.2858</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33947</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.32725</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.3533</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36687</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.40445</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.38173</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.25973</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38027</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35582</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41488</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36697</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36928</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.37975</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38486</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35987</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41718</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37029</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.3909</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.37985</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35207</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34882</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34525</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34639</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34258</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34153</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34262</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33253</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.34227</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34773</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36169</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33047</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32343</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33412</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32402</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.30877</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.39368</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.36379</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.34482</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.39455</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.43508</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.42575</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.46911</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.34821</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.39096</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.5185700000000001</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24953</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.27322</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.20783</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.2836</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.46758</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30272</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.21894</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.33356</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.30099</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.31345</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.31068</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.30974</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.4542</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.35455</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.35767</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.41487</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.34769</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35284</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31568</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.40525</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.33501</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.43452</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.41673</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.6898</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36215</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.33151</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.50979</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.22197</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37889</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30176</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32602</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.33166</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.31315</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.34904</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.31246</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.3145</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.39503</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.34929</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.33841</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32741</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.34179</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32677</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32653</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32502</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.3197</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32604</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.32984</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.33955</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33397</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33419</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34346</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34795</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.32715</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34114</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.30935</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.14674</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.19633</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.2922</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28342</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.29667</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.14503</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.18833</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.21985</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.22007</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.29227</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.31398</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32735</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31969</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.22084</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.29611</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.31286</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.31401</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.32728</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36374</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34983</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.34982</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.35195</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.34496</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.34285</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.34842</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35207</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.35592</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38527</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37151</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.3878</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37938</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.3495</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33933</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34909</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34922</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35792</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34686</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33673</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33932</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36881</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33639</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33928</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34914</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34914</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33616</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34821</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34024</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33636</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30872</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32627</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32826</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.19055</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31188</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.02742</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.02177</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.02612</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.02786</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32549</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>-0.00421</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>-0.004759999999999999</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.03725</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.02641</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.02677</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.0282</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>-0.04241</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.02746</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.02918</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.30508</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.02735</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.02904</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.18857</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.29116</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34496</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35373</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35447</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36618</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35934</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34559</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38203</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37849</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.3805</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38432</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.41705</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41134</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37908</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37551</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65639</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.7699600000000001</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.45173</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.28088</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45745</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.3523</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34423</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41093</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37609</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37062</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36184</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35899</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35878</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35591</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35188</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35899</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35928</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35961</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37025</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35859</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35632</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37857</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36569</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37968</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35629</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.3577</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34929</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31943</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26555</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14847</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.02302</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.01847</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.01896</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.1998</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.01467</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27986</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28031</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.21635</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.25543</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28494</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27718</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28945</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.28988</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30439</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.31133</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32161</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.22794</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29769</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.29268</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33178</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.33241</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.34762</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31588</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.36241</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.3484</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31876</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.35792</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43251</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38193</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.4144</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.64044</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.59796</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6058</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.48602</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.81174</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.48751</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.8132</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.44339</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.48961</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40074</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.36483</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.4709100000000001</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42989</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41854</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37822</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37463</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36697</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35984</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.48854</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.52696</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.47951</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.48233</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.4162</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39676</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40224</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.40949</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40748</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41577</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39829</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39437</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.38416</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40795</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.3829</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.36594</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.38376</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.3876</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41644</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38999</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.3996</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.36257</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.38354</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.37066</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.3757799999999999</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.38504</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.35507</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.36227</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.35302</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.3543</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.04069</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.40981</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.4464</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.43839</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.09404999999999999</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.07365000000000001</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.02277</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.03336</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.03736</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.05143</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>-0.01524</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.17913</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.20452</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.03643</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>-0.01674</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>-0.01396</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.03689</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>-0.03586</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>-0.01169</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>-0.04035</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>-0.04217</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>-0.04334</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>-0.04456</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>-0.04725</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>-0.04879</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>-0.0189</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.2206</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.21989</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.2213</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.33871</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35308</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.36634</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.43608</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.49195</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43808</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.50207</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.50526</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.5432899999999999</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.69096</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.71216</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.92347</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.53807</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.80624</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.58235</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.52497</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.83145</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7700900000000001</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6234299999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.67213</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.44138</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47168</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.48172</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47617</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.46892</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41674</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5512</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42742</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44114</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45505</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43406</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42403</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.4449</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41575</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39856</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45399</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.3969</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.4039700000000001</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.3959</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38557</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37751</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37261</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36565</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37425</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37061</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35953</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36565</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38563</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.38957</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37919</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36584</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36106</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.3634</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.27554</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.23817</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.28174</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.2794</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.27109</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.27362</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.22162</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.02913</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>-0.04342</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.05037</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.19708</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.0422</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>-0.0005200000000000001</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>-0.02313</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>-0.03415</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.00775</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>-0.03696</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.01253</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>-0.03816</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>-0.02672</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>-0.02538</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.04911</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>-0.03333</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.02919</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.02775</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.05866</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.03389</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.21807</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.23149</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.23174</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.23773</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.36205</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.38544</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.37039</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43288</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41576</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41492</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38367</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.3769</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38565</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39084</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40882</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40931</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.3455299999999999</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37113</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37591</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39606</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37884</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35488</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39911</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.37918</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37457</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.35886</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39476</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36515</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.32872</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44385</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36102</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39735</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39279</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35589</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37837</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37657</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35602</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35683</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35343</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34917</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35723</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34534</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34836</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33427</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.32861</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.32736</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.32725</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33534</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31698</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31569</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31276</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.30398</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.25436</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.26498</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.26302</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.26347</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22576</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.25756</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.22982</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.22302</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.24916</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.2264</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13953</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.25348</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.22236</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.22091</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.01141</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04307</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25008</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.22411</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.16928</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18743</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.23357</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30114</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.23381</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.23394</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.2031</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>-0.004860000000000001</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.19103</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.19973</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.17361</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.21081</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.21817</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.17127</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.21527</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.21684</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35256</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.31171</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.32381</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33079</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.38275</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.33649</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.34758</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.34604</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36307</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.3564</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.36846</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36332</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37804</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.35742</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.3579</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34567</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34687</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.33892</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33643</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34231</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33725</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.32583</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31672</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30432</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30708</v>
+      </c>
+      <c r="N136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.22413</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.21667</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.21669</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.29613</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.29613</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.22374</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.29503</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.29613</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.29652</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.29988</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.27963</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.20556</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.19331</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.04944</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.04945</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04946</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>-0.04987</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.04952</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04945</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04948</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.03867</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04142</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.03895000000000001</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04828</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04786</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.04720000000000001</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.03856</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.0495</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04948</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04949</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04928</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00067</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.25238</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04953</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04925</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04949</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.04642</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.02164</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04947</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04945</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03774</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.19017</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.24797</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.2756</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27981</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.30103</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.30475</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.21432</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.22631</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.33394</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.21412</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.21282</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.24826</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.22564</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.22568</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.30314</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.29867</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.37846</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33934</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.30048</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.29833</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.29468</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.13686</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.22545</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.537</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.21835</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.26461</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.4039700000000001</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.25201</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.33322</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.30309</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.27737</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.31303</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.29136</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.28778</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.28485</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.28843</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.2746</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.29098</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.26997</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.26641</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.29418</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.30928</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.28358</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.2941</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.28909</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.33402</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.04245</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.34262</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.3045</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.26964</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.2589</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.6284299999999999</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.7611599999999999</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.75238</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.5777</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.23312</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.30565</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.02744</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.22639</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.17731</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.20031</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.19969</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.1743</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.01104</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.004099999999999999</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.03028</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.03009</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.01101</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.04463</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>-0.04706</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.04819</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>-0.04823</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.20835</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.20846</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.01534</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.17995</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.19201</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.18709</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.16009</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25656</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.22344</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.26047</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.27015</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.27257</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.30347</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32502</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33212</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32917</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35468</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.36697</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.37593</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.36468</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.42429</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.36366</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.36776</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.35287</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.36097</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35233</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35429</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36445</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.36355</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33676</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32153</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35185</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.35692</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.3001</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.37891</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.37511</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.37412</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.36208</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.33955</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34639</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.3418</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.15188</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.33328</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32598</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33627</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.34196</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.52022</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.53128</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.36759</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.41516</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.29239</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.41938</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.41817</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.36074</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.22457</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.24355</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.37652</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.03801</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>-0.01619</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.0561</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>-0.01187</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.03079</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.03518</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.22882</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14177</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27688</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27025</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30546</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.23147</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.29693</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.29462</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.19573</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.22374</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.22965</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.22145</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.30648</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.29347</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.29352</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.33356</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.35557</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34883</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.38313</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36327</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.37907</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.41895</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.40084</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.36971</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.35605</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35631</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.38053</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36298</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.42327</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.35261</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34039</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.83428</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.38924</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.35944</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.37612</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.35351</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.39538</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.35281</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35444</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.34682</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.34929</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.35198</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.33847</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36736</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.3765</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36778</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35802</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35802</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.36055</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.35735</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.36338</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.54172</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.39439</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.24554</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36471</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.32463</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.22562</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.22876</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.22609</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.19492</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.27878</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.19654</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.02067</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.03821</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.0357</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.2284</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.02058</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.03904999999999999</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.18715</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.18584</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.19366</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.03929999999999999</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.03151</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.03994</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.03878</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.03965999999999999</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.02982</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.17671</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.04387</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.23111</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39362</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.21107</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.25977</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.45197</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.3332</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.45807</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.35799</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.38728</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.40049</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.35792</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.44621</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.37171</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.34922</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.3717</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.38086</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41425</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.36703</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.36139</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.3772</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.36713</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.36448</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.36618</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.27522</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.32231</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.32903</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.30951</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.38664</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.36806</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.36924</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.36604</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.34219</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.36187</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.36251</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36061</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.31335</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.28562</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35861</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.32766</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.31315</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.31745</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.18374</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.31674</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.28832</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.35821</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.28241</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.36583</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.28119</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.03999</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.23363</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.28671</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.23378</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.18183</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.2186</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.21543</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.2399</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.28816</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.44735</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.39008</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.37114</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.2256</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.22622</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.02795</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.18886</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.03182</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.04417</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.04284</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.04356</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.19649</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.23131</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.02995</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.31552</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.02242</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.03621</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.03982</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.03225</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.19747</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.23772</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.23033</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.22881</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.04797</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.20033</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.24764</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.33283</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.05504999999999999</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36871</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.22949</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.29463</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.29619</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.38306</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.38371</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.40618</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.41567</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.40584</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.39899</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.40037</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.41535</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.40114</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.43902</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.39133</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.38143</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.4212</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.41802</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.7445499999999999</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.40244</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.41704</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.39793</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.36721</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.37607</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.36706</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.33691</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.36075</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.33505</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.33605</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.22295</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36102</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.34544</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.35767</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34326</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.30583</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.2876</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34277</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.30762</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.30537</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.31301</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.30729</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.3142799999999999</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.21663</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.26385</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.28878</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.02999</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.29652</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.2186</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.21743</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.22634</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.30538</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.30604</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.30897</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.30821</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.30264</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.22835</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.29152</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.22614</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.22074</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.23298</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.02497</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.0394</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.22465</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.27224</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.22681</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.19907</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.009849999999999999</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.02878</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.21348</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>-0.00886</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.21097</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.02942</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.05404999999999999</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.01985</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.00238</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.01854</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.30212</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26342</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.00732</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>-0.01574</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.0207</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.0309</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.22674</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.08731999999999999</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.008840000000000001</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.01791</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.01227</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.01132</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.04156</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.04385</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.04811</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.04497</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.23567</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.24207</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.05368999999999999</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.05829</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.20302</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.18727</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.23705</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.22594</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.24944</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.30331</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.3797</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.38231</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.38373</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.34809</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.38367</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.37521</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.29153</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.33619</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.3287</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.21956</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.21943</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.21691</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.16921</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.21456</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.21935</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.47377</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.36313</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.45926</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.21732</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.36987</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33842</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34751</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.31195</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.31099</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.30698</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.21753</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.28637</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.33362</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.32263</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.30638</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.3137799999999999</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.22741</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.22605</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.2201</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.21912</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.04349</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.23729</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.20213</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.05302</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>-0.03669</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>-0.03749</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>-0.03896</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.36547</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.04548</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.1911</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>-0.02883</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.06236999999999999</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>-0.01461</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.04968</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>-0.04679999999999999</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>-0.04911</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.02172</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.49781</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.24281</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.30135</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.23726</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.2383</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.31407</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.29615</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.29475</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.31677</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.34976</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.34304</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.37714</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.3723</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39034</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36457</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38277</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.49939</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.37715</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.37506</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37675</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38179</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.36122</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.38273</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.36034</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.35635</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.22117</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.34248</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33493</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.31139</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.32738</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.30015</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.37876</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.37875</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37576</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.37332</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.30558</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.28808</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.32965</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.34367</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33835</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33328</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.34573</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35245</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34751</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.28681</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.02649</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.21954</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.18509</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.2198</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.21957</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.01853</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.0371</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>-0.02041</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>-0.009949999999999999</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.04561</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.04699</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.04756000000000001</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.02432</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>-0.03261</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.09616</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.07006</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>-0.04969</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.08758000000000001</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>-0.04721</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.05467</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.05172</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>-0.01184</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.03235</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.04129</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.22233</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.22194</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.21927</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.22197</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.29847</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.23463</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.34762</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.34711</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.36406</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37103</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.37969</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.37426</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.38505</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.40153</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.47467</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.38927</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.39057</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.38324</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.38756</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.3798</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38543</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37708</v>
       </c>
     </row>
   </sheetData>
